--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/OKLAHOMA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/OKLAHOMA_2017.xlsx
@@ -661,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="18">
@@ -877,7 +877,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="30">
@@ -1471,7 +1471,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="63">
@@ -1849,7 +1849,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="84">
@@ -3181,7 +3181,7 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="158">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C161">
@@ -3775,7 +3775,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="191">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C255">
@@ -5953,7 +5953,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="312">
@@ -6133,7 +6133,7 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="322">
@@ -7051,7 +7051,7 @@
         <v>7</v>
       </c>
       <c r="D372">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="373">
@@ -7177,7 +7177,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="380">
@@ -7393,7 +7393,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="392">
@@ -8221,7 +8221,7 @@
         <v>7</v>
       </c>
       <c r="D437">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="438">
@@ -8347,7 +8347,7 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="445">
@@ -8887,7 +8887,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="475">
@@ -8995,7 +8995,7 @@
         <v>7</v>
       </c>
       <c r="D480">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="481">
@@ -10687,7 +10687,7 @@
         <v>7</v>
       </c>
       <c r="D574">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="575">
@@ -10795,7 +10795,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="581">
@@ -10885,7 +10885,7 @@
         <v>7</v>
       </c>
       <c r="D585">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="586">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C600">
@@ -14917,7 +14917,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="810">
@@ -15799,7 +15799,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="859">
@@ -16213,7 +16213,7 @@
         <v>7</v>
       </c>
       <c r="D881">
-        <v>0.0009669843901091311</v>
+        <v>0.0009669843901091312</v>
       </c>
     </row>
     <row r="882">
@@ -17023,7 +17023,7 @@
         <v>71</v>
       </c>
       <c r="D926">
-        <v>0.009807984528249759</v>
+        <v>0.00980798452824976</v>
       </c>
     </row>
     <row r="927">
